--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.92572124957</v>
+        <v>46157.93110785987</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93110785987</v>
+        <v>46157.93178861427</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93178861427</v>
+        <v>46157.93403664406</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93403664406</v>
+        <v>46157.93721681504</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46157.93721681504</v>
+        <v>46158.28219629348</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.28219629348</v>
+        <v>46158.29694564662</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29694564662</v>
+        <v>46158.29819104145</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.29819104145</v>
+        <v>46158.3339072982</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.3339072982</v>
+        <v>46158.36860455764</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">

--- a/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
+++ b/Дело3а-78-2026Таганай/01_Иск/01.13_Банковские_платежи_и_счета/Для суда от Виктории/Для СУДА/27. САО РЕСО-Гарантия (нет счетов на оплату)/2024 год/Сводная_ведомость.xlsx
@@ -651,7 +651,7 @@
         </is>
       </c>
       <c r="I6" s="7" t="n">
-        <v>46158.36860455764</v>
+        <v>46158.37291175118</v>
       </c>
     </row>
     <row r="7" ht="15" customHeight="1">
